--- a/data/trans_orig/P04C05_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04C05_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con refrigeración por aire acondicionado mediante aparatos fijos en la vivienda en 2023</t>
+          <t>Población según si dispone de refrigeración por aire acondicionado mediante aparatos fijos en la vivienda en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>162234</t>
+          <t>162954</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>201926</t>
+          <t>204811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>247062</t>
+          <t>245829</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285978</t>
+          <t>288784</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>417353</t>
+          <t>420395</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>476980</t>
+          <t>477765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>16315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32797</t>
+          <t>34456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>298336</t>
+          <t>297277</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>338409</t>
+          <t>337833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>457324</t>
+          <t>456537</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>496939</t>
+          <t>499491</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>768531</t>
+          <t>765538</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>826363</t>
+          <t>824976</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,07%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>328378</t>
+          <t>317515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>552881</t>
+          <t>552643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>413973</t>
+          <t>413493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>703530</t>
+          <t>689509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>831298</t>
+          <t>849585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1209972</t>
+          <t>1202478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,82 +1314,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>14065</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>22106</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>35857</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>26135</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>48997</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>14065</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>8578</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>21534</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>35857</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>24486</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>49247</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1713525</t>
+          <t>1715476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1945344</t>
+          <t>1960211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1516974</t>
+          <t>1533026</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1808723</t>
+          <t>1812431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3275802</t>
+          <t>3286890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3660145</t>
+          <t>3646899</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100129</t>
+          <t>100205</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141355</t>
+          <t>141924</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126155</t>
+          <t>127410</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164570</t>
+          <t>165377</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>237860</t>
+          <t>236495</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>294453</t>
+          <t>293533</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>22874</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>498280</t>
+          <t>499026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>540834</t>
+          <t>541505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>487660</t>
+          <t>486724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>526439</t>
+          <t>525537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1000408</t>
+          <t>999198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1057408</t>
+          <t>1056340</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,91%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>600292</t>
+          <t>592903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>859338</t>
+          <t>863001</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>805687</t>
+          <t>809237</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1108126</t>
+          <t>1107023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1491019</t>
+          <t>1531425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1905408</t>
+          <t>1908696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>29220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55278</t>
+          <t>56665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23770</t>
+          <t>22982</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43039</t>
+          <t>41494</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57152</t>
+          <t>56596</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90647</t>
+          <t>91344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2547228</t>
+          <t>2543078</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2820338</t>
+          <t>2824176</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2517542</t>
+          <t>2511483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2819477</t>
+          <t>2810827</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5116129</t>
+          <t>5116292</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5534414</t>
+          <t>5499334</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04C05_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04C05_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>182073</t>
+          <t>215406</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>162954</t>
+          <t>193799</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204811</t>
+          <t>237715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>266111</t>
+          <t>284387</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>245829</t>
+          <t>264518</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>288784</t>
+          <t>307821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>448184</t>
+          <t>499793</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>420395</t>
+          <t>467230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>477765</t>
+          <t>530963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,98%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11028</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>18769</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23461</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34456</t>
+          <t>37710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>318439</t>
+          <t>345726</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>297277</t>
+          <t>320886</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>337833</t>
+          <t>368196</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>477738</t>
+          <t>524615</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>456537</t>
+          <t>501430</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>499491</t>
+          <t>544705</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>796177</t>
+          <t>870341</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>765538</t>
+          <t>839151</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>824976</t>
+          <t>899204</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,33%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>512945</t>
+          <t>576501</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>512945</t>
+          <t>576501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>512945</t>
+          <t>576501</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>754877</t>
+          <t>821348</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>754877</t>
+          <t>821348</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>754877</t>
+          <t>821348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1267822</t>
+          <t>1397850</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1267822</t>
+          <t>1397850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1267822</t>
+          <t>1397850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>475963</t>
+          <t>541108</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>317515</t>
+          <t>498207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>552643</t>
+          <t>594170</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>551429</t>
+          <t>561438</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>413493</t>
+          <t>521986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>689509</t>
+          <t>601134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1027392</t>
+          <t>1102546</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>849585</t>
+          <t>1036751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1202478</t>
+          <t>1168818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32800</t>
+          <t>44234</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22106</t>
+          <t>33409</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>35857</t>
+          <t>51949</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26135</t>
+          <t>40025</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48997</t>
+          <t>67991</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1792572</t>
+          <t>1658864</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1715476</t>
+          <t>1604319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1960211</t>
+          <t>1703647</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1668936</t>
+          <t>1584996</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1533026</t>
+          <t>1544272</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1812431</t>
+          <t>1626181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3461508</t>
+          <t>3243861</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3286890</t>
+          <t>3178494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3646899</t>
+          <t>3309055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>75,23%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2234430</t>
+          <t>2167789</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2234430</t>
+          <t>2167789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2234430</t>
+          <t>2167789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4524757</t>
+          <t>4398356</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4524757</t>
+          <t>4398356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4524757</t>
+          <t>4398356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>119230</t>
+          <t>145407</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100205</t>
+          <t>123492</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141924</t>
+          <t>170611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145398</t>
+          <t>167431</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>127410</t>
+          <t>147968</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165377</t>
+          <t>188727</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>264628</t>
+          <t>312838</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236495</t>
+          <t>282172</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>293533</t>
+          <t>346708</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22874</t>
+          <t>24062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>521231</t>
+          <t>558610</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>499026</t>
+          <t>533406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>541505</t>
+          <t>581020</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>506722</t>
+          <t>557859</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>486724</t>
+          <t>536038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>525537</t>
+          <t>578356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1027953</t>
+          <t>1116469</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>999198</t>
+          <t>1082657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1056340</t>
+          <t>1147339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>658959</t>
+          <t>732477</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>658959</t>
+          <t>732477</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>658959</t>
+          <t>732477</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1305582</t>
+          <t>1444064</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1305582</t>
+          <t>1444064</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1305582</t>
+          <t>1444064</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>777266</t>
+          <t>901922</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>592903</t>
+          <t>840024</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>863001</t>
+          <t>959868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>962937</t>
+          <t>1013256</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>809237</t>
+          <t>960982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1107023</t>
+          <t>1062482</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1740204</t>
+          <t>1915177</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1531425</t>
+          <t>1836015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1908696</t>
+          <t>1988746</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40386</t>
+          <t>53533</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29220</t>
+          <t>41037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56665</t>
+          <t>70984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31932</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22982</t>
+          <t>31382</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41494</t>
+          <t>52988</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>94422</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56596</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91344</t>
+          <t>114461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2632242</t>
+          <t>2563200</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2543078</t>
+          <t>2502455</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2824176</t>
+          <t>2621033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2653396</t>
+          <t>2667470</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2511483</t>
+          <t>2619310</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2810827</t>
+          <t>2718207</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5285639</t>
+          <t>5230671</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5116292</t>
+          <t>5151156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5499334</t>
+          <t>5306973</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3449895</t>
+          <t>3518655</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3449895</t>
+          <t>3518655</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3449895</t>
+          <t>3518655</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3648265</t>
+          <t>3721615</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3648265</t>
+          <t>3721615</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3648265</t>
+          <t>3721615</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7098161</t>
+          <t>7240270</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7098161</t>
+          <t>7240270</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7098161</t>
+          <t>7240270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
